--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9570,0.0139,0.0080,0.0109</t>
-  </si>
-  <si>
-    <t>0.0332,0.0026,0.0017,0.9860</t>
-  </si>
-  <si>
-    <t>0.9918,0.0015,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.2961,0.0015,0.0032,0.8369</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0040,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0003,0.0003</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9675,0.0127,0.0061,0.0048</t>
+  </si>
+  <si>
+    <t>0.0424,0.0033,0.0135,0.9648</t>
+  </si>
+  <si>
+    <t>0.9772,0.0038,0.0009,0.0107</t>
+  </si>
+  <si>
+    <t>0.1821,0.0122,0.0097,0.8765</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0018,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0015,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0035,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9433,0.0036,0.0764,0.0013</t>
+  </si>
+  <si>
+    <t>0.0195,0.0284,0.9725,0.0027</t>
+  </si>
+  <si>
+    <t>0.1218,0.0049,0.9369,0.0002</t>
+  </si>
+  <si>
+    <t>0.2994,0.0059,0.8101,0.0012</t>
+  </si>
+  <si>
+    <t>0.9576,0.0031,0.0504,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.9957,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0135,0.9801,0.0135,0.0005</t>
+  </si>
+  <si>
+    <t>0.0582,0.9583,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.9897,0.0068,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.9941,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.8579,0.0093,0.1216,0.0130</t>
+  </si>
+  <si>
+    <t>0.3774,0.0595,0.4949,0.1412</t>
+  </si>
+  <si>
+    <t>0.0075,0.0011,0.9946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0375,0.0175,0.9230,0.0254</t>
+  </si>
+  <si>
+    <t>0.0844,0.0008,0.9586,0.0009</t>
+  </si>
+  <si>
+    <t>0.0230,0.0004,0.9858,0.0006</t>
+  </si>
+  <si>
+    <t>0.0121,0.0006,0.9908,0.0008</t>
+  </si>
+  <si>
+    <t>0.9036,0.1801,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.6638,0.3012,0.0572,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0111,0.9900,0.0115</t>
+  </si>
+  <si>
+    <t>0.0071,0.7623,0.5405,0.0001</t>
+  </si>
+  <si>
+    <t>0.9287,0.0457,0.0177,0.0077</t>
+  </si>
+  <si>
+    <t>0.9802,0.0084,0.0092,0.0001</t>
+  </si>
+  <si>
+    <t>0.5495,0.6081,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.9862,0.0158,0.0043</t>
+  </si>
+  <si>
+    <t>0.0528,0.7709,0.0653,0.0165</t>
+  </si>
+  <si>
+    <t>0.0094,0.0012,0.9906,0.0015</t>
+  </si>
+  <si>
+    <t>0.0460,0.0194,0.9639,0.0008</t>
+  </si>
+  <si>
+    <t>0.2508,0.0009,0.7102,0.0076</t>
+  </si>
+  <si>
+    <t>0.0173,0.0736,0.9691,0.0022</t>
+  </si>
+  <si>
+    <t>0.0015,0.9946,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0121,0.9977,0.0007</t>
+  </si>
+  <si>
+    <t>0.0387,0.5978,0.0534,0.7728</t>
+  </si>
+  <si>
+    <t>0.0041,0.9893,0.0018,0.0021</t>
+  </si>
+  <si>
+    <t>0.0014,0.9951,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.9969,0.0136,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.1263,0.9608,0.0025</t>
+  </si>
+  <si>
+    <t>0.0013,0.2993,0.9899,0.0006</t>
+  </si>
+  <si>
+    <t>0.0020,0.0067,0.9937,0.0011</t>
+  </si>
+  <si>
+    <t>0.0174,0.0023,0.9836,0.0015</t>
+  </si>
+  <si>
+    <t>0.0329,0.0131,0.9710,0.0008</t>
+  </si>
+  <si>
+    <t>0.0056,0.3176,0.9432,0.0012</t>
+  </si>
+  <si>
+    <t>0.9840,0.0173,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9876,0.0062,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.9270,0.0250,0.0542,0.0103</t>
+  </si>
+  <si>
+    <t>0.0016,0.0964,0.9904,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0047,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9885,0.0124,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.8897,0.9686,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.2908,0.9852,0.0007</t>
+  </si>
+  <si>
+    <t>0.0096,0.2605,0.9774,0.0025</t>
+  </si>
+  <si>
+    <t>0.0001,0.9705,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.0293,0.9876,0.0008</t>
+  </si>
+  <si>
+    <t>0.0420,0.9676,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.9959,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7632,0.0309,0.3452,0.0043</t>
+  </si>
+  <si>
+    <t>0.9083,0.0673,0.0310,0.0070</t>
+  </si>
+  <si>
+    <t>0.0018,0.0069,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.8338,0.9685,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9805,0.8636,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9929,0.0435,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9861,0.5836,0.0005</t>
+  </si>
+  <si>
+    <t>0.0137,0.0008,0.0015,0.9937</t>
+  </si>
+  <si>
+    <t>0.0040,0.0029,0.0006,0.9966</t>
+  </si>
+  <si>
+    <t>0.0075,0.0004,0.0005,0.9960</t>
+  </si>
+  <si>
+    <t>0.0371,0.0038,0.0017,0.9828</t>
+  </si>
+  <si>
+    <t>0.0177,0.0021,0.0032,0.9889</t>
+  </si>
+  <si>
+    <t>0.0084,0.0016,0.0004,0.9956</t>
+  </si>
+  <si>
+    <t>0.0009,0.9564,0.9441,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9237,0.9855,0.0003</t>
+  </si>
+  <si>
+    <t>0.0083,0.9651,0.0247,0.0027</t>
+  </si>
+  <si>
+    <t>0.0038,0.8752,0.8899,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9761,0.8686,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.8786,0.5605,0.0037</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9894,0.0250,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9881,0.0195,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9899,0.0159,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0046,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9886,0.0166,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9896,0.0093,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0017,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0231,0.0058,0.9716,0.0007</t>
+  </si>
+  <si>
+    <t>0.0143,0.0051,0.9822,0.0027</t>
+  </si>
+  <si>
+    <t>0.8707,0.0073,0.0919,0.0063</t>
+  </si>
+  <si>
+    <t>0.0245,0.0028,0.9845,0.0007</t>
+  </si>
+  <si>
+    <t>0.0016,0.9967,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9962,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0059,0.9893,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.0176,0.9762,0.0135,0.0011</t>
+  </si>
+  <si>
+    <t>0.0099,0.9874,0.0031,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.9971,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9033,0.0907,0.0232,0.0015</t>
+  </si>
+  <si>
+    <t>0.7040,0.1059,0.2324,0.0053</t>
+  </si>
+  <si>
+    <t>0.9763,0.0012,0.0263,0.0002</t>
+  </si>
+  <si>
+    <t>0.7492,0.0051,0.3249,0.0070</t>
+  </si>
+  <si>
+    <t>0.3703,0.0151,0.6924,0.0031</t>
+  </si>
+  <si>
+    <t>0.0353,0.0462,0.1140,0.9007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0119,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9940,0.0261,0.0282</t>
+  </si>
+  <si>
+    <t>0.0002,0.9924,0.9101,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9949,0.0211,0.0004</t>
+  </si>
+  <si>
+    <t>0.9403,0.0999,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.5094,0.5389,0.0406,0.0011</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9645,0.0152,0.0208,0.0026</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0073,0.0060,0.0044</t>
+  </si>
+  <si>
+    <t>0.9804,0.0082,0.0041,0.0037</t>
+  </si>
+  <si>
+    <t>0.0044,0.8748,0.8812,0.0021</t>
+  </si>
+  <si>
+    <t>0.0040,0.7400,0.9316,0.0005</t>
+  </si>
+  <si>
+    <t>0.0170,0.0302,0.9596,0.0014</t>
+  </si>
+  <si>
+    <t>0.1427,0.0070,0.9247,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0007,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.7213,0.0025,0.4123,0.0034</t>
+  </si>
+  <si>
+    <t>0.2321,0.0014,0.9216,0.0007</t>
+  </si>
+  <si>
+    <t>0.9469,0.0075,0.0435,0.0008</t>
+  </si>
+  <si>
+    <t>0.7164,0.0004,0.0004,0.5684</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0059,0.9981</t>
+  </si>
+  <si>
+    <t>0.0029,0.0121,0.0004,0.9967</t>
+  </si>
+  <si>
+    <t>0.0632,0.0001,0.0003,0.9836</t>
+  </si>
+  <si>
+    <t>0.0039,0.9639,0.1476,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.9931,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9922,0.0010,0.0014,0.0019</t>
+  </si>
+  <si>
+    <t>0.6544,0.4442,0.0145,0.0012</t>
+  </si>
+  <si>
+    <t>0.9907,0.0017,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.2778,0.0101,0.0035,0.7553</t>
+  </si>
+  <si>
+    <t>0.9905,0.0026,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.0164,0.0252,0.9104,0.1099</t>
+  </si>
+  <si>
+    <t>0.3155,0.0006,0.0037,0.8288</t>
+  </si>
+  <si>
+    <t>0.9836,0.0017,0.0031,0.0061</t>
+  </si>
+  <si>
+    <t>0.3582,0.6638,0.0282,0.0210</t>
+  </si>
+  <si>
+    <t>0.9906,0.0049,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9757,0.0227,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.5216,0.5230,0.0628,0.0037</t>
+  </si>
+  <si>
+    <t>0.9023,0.0459,0.0553,0.0021</t>
+  </si>
+  <si>
+    <t>0.9934,0.0009,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0034,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0020,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9883,0.0178,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0011,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.8491,0.2578,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.8062,0.3180,0.0043,0.0006</t>
+  </si>
+  <si>
+    <t>0.6552,0.5222,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.8059,0.1148,0.1550,0.0231</t>
+  </si>
+  <si>
+    <t>0.9842,0.0193,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9870,0.0069,0.0040,0.0006</t>
+  </si>
+  <si>
+    <t>0.9919,0.0044,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9388,0.0938,0.0060,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0726,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.9740,0.0119,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.0093,0.0090,0.9862,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.0235,0.9906,0.0033</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9958,0.0039</t>
+  </si>
+  <si>
+    <t>0.0595,0.0586,0.9075,0.0007</t>
+  </si>
+  <si>
+    <t>0.0041,0.0040,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0019,0.9956,0.0019</t>
+  </si>
+  <si>
+    <t>0.0151,0.0035,0.9876,0.0008</t>
+  </si>
+  <si>
+    <t>0.0299,0.0153,0.9497,0.0231</t>
+  </si>
+  <si>
+    <t>0.0429,0.0082,0.9678,0.0015</t>
+  </si>
+  <si>
+    <t>0.3162,0.5489,0.1722,0.0171</t>
+  </si>
+  <si>
+    <t>0.3287,0.0622,0.6393,0.0017</t>
+  </si>
+  <si>
+    <t>0.2722,0.3275,0.4578,0.0198</t>
+  </si>
+  <si>
+    <t>0.1439,0.0832,0.8318,0.0068</t>
+  </si>
+  <si>
+    <t>0.8220,0.0065,0.3387,0.0017</t>
+  </si>
+  <si>
+    <t>0.1412,0.0389,0.8487,0.0056</t>
+  </si>
+  <si>
+    <t>0.0469,0.9606,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.3126,0.8414,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9098,0.2210,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9373,0.0771,0.0125,0.0005</t>
+  </si>
+  <si>
+    <t>0.4028,0.7820,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.8217,0.0877,0.1225,0.0084</t>
+  </si>
+  <si>
+    <t>0.9955,0.0002,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.8762,0.0043,0.1213,0.0057</t>
+  </si>
+  <si>
+    <t>0.9504,0.0117,0.0266,0.0095</t>
+  </si>
+  <si>
+    <t>0.3270,0.0217,0.7163,0.0088</t>
+  </si>
+  <si>
+    <t>0.0411,0.0222,0.9316,0.0069</t>
+  </si>
+  <si>
+    <t>0.0367,0.0746,0.8859,0.0162</t>
+  </si>
+  <si>
+    <t>0.1105,0.0305,0.8540,0.0152</t>
+  </si>
+  <si>
+    <t>0.3519,0.0067,0.6782,0.0053</t>
+  </si>
+  <si>
+    <t>0.0007,0.0392,0.9965,0.0006</t>
   </si>
   <si>
     <t>0.9979,0.0023,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9984,0.0010,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.8918,0.0042,0.1784,0.0017</t>
-  </si>
-  <si>
-    <t>0.0375,0.0060,0.9733,0.0010</t>
-  </si>
-  <si>
-    <t>0.4330,0.0022,0.7966,0.0004</t>
-  </si>
-  <si>
-    <t>0.0409,0.0133,0.9560,0.0022</t>
-  </si>
-  <si>
-    <t>0.9701,0.0007,0.0591,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.9953,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.9980,0.0131,0.0002</t>
-  </si>
-  <si>
-    <t>0.0518,0.9631,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.0096,0.9843,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.0015,0.9963,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9002,0.0060,0.1143,0.0028</t>
-  </si>
-  <si>
-    <t>0.6804,0.0019,0.2677,0.0116</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9983,0.0005</t>
-  </si>
-  <si>
-    <t>0.0393,0.0168,0.9567,0.0049</t>
-  </si>
-  <si>
-    <t>0.0271,0.0039,0.9629,0.0132</t>
-  </si>
-  <si>
-    <t>0.0078,0.0017,0.9872,0.0043</t>
-  </si>
-  <si>
-    <t>0.0075,0.0021,0.9903,0.0027</t>
-  </si>
-  <si>
-    <t>0.7001,0.4303,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.2017,0.8450,0.0251,0.0039</t>
-  </si>
-  <si>
-    <t>0.0005,0.0093,0.9923,0.0258</t>
-  </si>
-  <si>
-    <t>0.0050,0.9881,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9788,0.0079,0.0085,0.0006</t>
-  </si>
-  <si>
-    <t>0.9695,0.0153,0.0101,0.0007</t>
-  </si>
-  <si>
-    <t>0.7555,0.3326,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.0092,0.9742,0.2196,0.0060</t>
-  </si>
-  <si>
-    <t>0.2359,0.3166,0.2691,0.0158</t>
-  </si>
-  <si>
-    <t>0.0322,0.0078,0.9722,0.0022</t>
-  </si>
-  <si>
-    <t>0.0271,0.0059,0.9782,0.0011</t>
-  </si>
-  <si>
-    <t>0.2663,0.0011,0.7700,0.0054</t>
-  </si>
-  <si>
-    <t>0.0063,0.0102,0.9909,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9971,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0135,0.9965,0.0007</t>
-  </si>
-  <si>
-    <t>0.0751,0.5120,0.0490,0.7380</t>
-  </si>
-  <si>
-    <t>0.0068,0.9795,0.0086,0.0057</t>
-  </si>
-  <si>
-    <t>0.0005,0.9972,0.0423,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9974,0.0261,0.0007</t>
-  </si>
-  <si>
-    <t>0.0024,0.0177,0.9917,0.0008</t>
-  </si>
-  <si>
-    <t>0.0035,0.2868,0.9881,0.0010</t>
-  </si>
-  <si>
-    <t>0.0889,0.0116,0.9357,0.0004</t>
-  </si>
-  <si>
-    <t>0.0280,0.0016,0.9815,0.0005</t>
-  </si>
-  <si>
-    <t>0.0260,0.0079,0.9778,0.0017</t>
-  </si>
-  <si>
-    <t>0.0029,0.0341,0.9818,0.0029</t>
-  </si>
-  <si>
-    <t>0.9870,0.0104,0.0015,0.0013</t>
-  </si>
-  <si>
-    <t>0.9810,0.0080,0.0109,0.0006</t>
-  </si>
-  <si>
-    <t>0.9930,0.0034,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.0508,0.9943,0.0059</t>
-  </si>
-  <si>
-    <t>0.9941,0.0013,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0084,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9879,0.0045,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.6329,0.9809,0.0007</t>
-  </si>
-  <si>
-    <t>0.0201,0.2539,0.9638,0.0056</t>
-  </si>
-  <si>
-    <t>0.0057,0.0073,0.9877,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.9621,0.9758,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.0085,0.9936,0.0032</t>
-  </si>
-  <si>
-    <t>0.0086,0.9931,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0243,0.9859,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9043,0.0075,0.1668,0.0017</t>
-  </si>
-  <si>
-    <t>0.4703,0.2821,0.4248,0.0081</t>
-  </si>
-  <si>
-    <t>0.0039,0.0102,0.9922,0.0010</t>
-  </si>
-  <si>
-    <t>0.0041,0.9099,0.4850,0.0062</t>
-  </si>
-  <si>
-    <t>0.0018,0.9097,0.8567,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9949,0.0929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.9430,0.8695,0.0015</t>
-  </si>
-  <si>
-    <t>0.0471,0.0010,0.0092,0.9632</t>
-  </si>
-  <si>
-    <t>0.0018,0.0008,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.0057,0.0004,0.0004,0.9972</t>
-  </si>
-  <si>
-    <t>0.0346,0.0009,0.0005,0.9881</t>
-  </si>
-  <si>
-    <t>0.0118,0.0011,0.0041,0.9907</t>
-  </si>
-  <si>
-    <t>0.0100,0.0017,0.0014,0.9930</t>
-  </si>
-  <si>
-    <t>0.0008,0.9770,0.9353,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.8969,0.9777,0.0003</t>
-  </si>
-  <si>
-    <t>0.0307,0.7233,0.6840,0.0096</t>
-  </si>
-  <si>
-    <t>0.0032,0.9367,0.8984,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9794,0.0411,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0094,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9745,0.0451,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0028,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9920,0.0095,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0079,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9926,0.0062,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0193,0.0014,0.9852,0.0007</t>
-  </si>
-  <si>
-    <t>0.3299,0.0060,0.8011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9040,0.0087,0.1338,0.0015</t>
-  </si>
-  <si>
-    <t>0.0180,0.0022,0.9855,0.0010</t>
-  </si>
-  <si>
-    <t>0.0186,0.9810,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.9950,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.0098,0.9839,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.0257,0.9594,0.0153,0.0034</t>
-  </si>
-  <si>
-    <t>0.0225,0.9751,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.0011,0.9975,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.5741,0.4482,0.0372,0.0012</t>
-  </si>
-  <si>
-    <t>0.1016,0.1134,0.8165,0.0211</t>
-  </si>
-  <si>
-    <t>0.2585,0.0028,0.8934,0.0004</t>
-  </si>
-  <si>
-    <t>0.5368,0.0970,0.4283,0.0136</t>
-  </si>
-  <si>
-    <t>0.8107,0.0058,0.3337,0.0022</t>
-  </si>
-  <si>
-    <t>0.0100,0.2862,0.0301,0.9255</t>
-  </si>
-  <si>
-    <t>0.0005,0.9973,0.0130,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.9930,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9980,0.0029,0.0024</t>
-  </si>
-  <si>
-    <t>0.0002,0.9701,0.9858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.9942,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.4641,0.6991,0.0079,0.0007</t>
-  </si>
-  <si>
-    <t>0.8632,0.1915,0.0078,0.0014</t>
-  </si>
-  <si>
-    <t>0.9959,0.0031,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0019,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0017,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0031,0.0047,0.0014</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9929,0.0035,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9769,0.0112,0.0047,0.0049</t>
-  </si>
-  <si>
-    <t>0.9915,0.0016,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.0055,0.4215,0.9678,0.0023</t>
-  </si>
-  <si>
-    <t>0.0052,0.4263,0.9131,0.0002</t>
-  </si>
-  <si>
-    <t>0.0293,0.0402,0.9676,0.0003</t>
-  </si>
-  <si>
-    <t>0.0142,0.0530,0.9626,0.0019</t>
-  </si>
-  <si>
-    <t>0.9761,0.0028,0.0116,0.0012</t>
-  </si>
-  <si>
-    <t>0.9140,0.0022,0.1614,0.0007</t>
-  </si>
-  <si>
-    <t>0.7424,0.0006,0.4586,0.0011</t>
-  </si>
-  <si>
-    <t>0.5567,0.0560,0.4716,0.0156</t>
-  </si>
-  <si>
-    <t>0.6352,0.0006,0.0001,0.6870</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.0008,0.9992</t>
-  </si>
-  <si>
-    <t>0.0015,0.0033,0.0005,0.9984</t>
-  </si>
-  <si>
-    <t>0.0295,0.0011,0.0009,0.9896</t>
-  </si>
-  <si>
-    <t>0.0010,0.9900,0.0391,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1075,0.9136,0.0032,0.0023</t>
-  </si>
-  <si>
-    <t>0.9943,0.0012,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.0600,0.9562,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9831,0.0030,0.0023,0.0070</t>
-  </si>
-  <si>
-    <t>0.1049,0.0160,0.1312,0.8297</t>
-  </si>
-  <si>
-    <t>0.9975,0.0007,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0089,0.0227,0.6166,0.6774</t>
-  </si>
-  <si>
-    <t>0.2846,0.0004,0.0215,0.5689</t>
-  </si>
-  <si>
-    <t>0.9829,0.0029,0.0012,0.0061</t>
-  </si>
-  <si>
-    <t>0.5658,0.5164,0.0134,0.0094</t>
-  </si>
-  <si>
-    <t>0.9958,0.0022,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0040,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6474,0.3816,0.0321,0.0012</t>
-  </si>
-  <si>
-    <t>0.9047,0.0255,0.0813,0.0014</t>
-  </si>
-  <si>
-    <t>0.9790,0.0058,0.0119,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0075,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.9893,0.0041,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.9947,0.0022,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9801,0.0139,0.0069,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0009,0.0014,0.0023</t>
-  </si>
-  <si>
-    <t>0.9954,0.0009,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.8872,0.1076,0.0129,0.0051</t>
-  </si>
-  <si>
-    <t>0.7556,0.4201,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.8609,0.2304,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.9010,0.0972,0.0318,0.0058</t>
-  </si>
-  <si>
-    <t>0.9955,0.0042,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9837,0.0050,0.0108,0.0007</t>
-  </si>
-  <si>
-    <t>0.9932,0.0032,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9671,0.0405,0.0033,0.0024</t>
-  </si>
-  <si>
-    <t>0.0006,0.0188,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.9762,0.0151,0.0062,0.0003</t>
-  </si>
-  <si>
-    <t>0.0058,0.0043,0.9931,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.1368,0.9922,0.0006</t>
-  </si>
-  <si>
-    <t>0.0139,0.0027,0.9873,0.0019</t>
-  </si>
-  <si>
-    <t>0.0122,0.0091,0.9838,0.0010</t>
-  </si>
-  <si>
-    <t>0.0079,0.0053,0.9942,0.0003</t>
-  </si>
-  <si>
-    <t>0.0027,0.0009,0.9967,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.0128,0.9931,0.0019</t>
-  </si>
-  <si>
-    <t>0.0653,0.0037,0.9544,0.0054</t>
-  </si>
-  <si>
-    <t>0.0565,0.0225,0.9397,0.0071</t>
-  </si>
-  <si>
-    <t>0.6203,0.0489,0.4531,0.0104</t>
-  </si>
-  <si>
-    <t>0.0989,0.4663,0.4451,0.0012</t>
-  </si>
-  <si>
-    <t>0.2583,0.2224,0.5120,0.0090</t>
-  </si>
-  <si>
-    <t>0.5910,0.0188,0.5010,0.0037</t>
-  </si>
-  <si>
-    <t>0.8449,0.0048,0.2600,0.0029</t>
-  </si>
-  <si>
-    <t>0.0746,0.0095,0.9339,0.0030</t>
-  </si>
-  <si>
-    <t>0.0975,0.9322,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.4340,0.7756,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8260,0.3748,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9944,0.0049,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.7423,0.4344,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.6687,0.3323,0.0274,0.0049</t>
-  </si>
-  <si>
-    <t>0.9873,0.0028,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.9629,0.0011,0.0388,0.0016</t>
-  </si>
-  <si>
-    <t>0.9290,0.0037,0.1007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9410,0.0038,0.0597,0.0015</t>
-  </si>
-  <si>
-    <t>0.0035,0.0020,0.9887,0.0041</t>
-  </si>
-  <si>
-    <t>0.0108,0.0084,0.9771,0.0046</t>
-  </si>
-  <si>
-    <t>0.0075,0.0182,0.9797,0.0059</t>
-  </si>
-  <si>
-    <t>0.1185,0.0032,0.8790,0.0072</t>
-  </si>
-  <si>
-    <t>0.0404,0.0099,0.9689,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0053,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0053,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9968,0.0015,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9715,0.0219,0.0084,0.0030</t>
-  </si>
-  <si>
-    <t>0.9968,0.0016,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9922,0.0040,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.0077,0.0963,0.9862,0.0017</t>
-  </si>
-  <si>
-    <t>0.0387,0.2082,0.9073,0.0084</t>
-  </si>
-  <si>
-    <t>0.9715,0.0075,0.0106,0.0017</t>
-  </si>
-  <si>
-    <t>0.0277,0.0028,0.9766,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0154,0.9943,0.0005</t>
-  </si>
-  <si>
-    <t>0.0254,0.0379,0.9589,0.0017</t>
-  </si>
-  <si>
-    <t>0.0024,0.0058,0.9955,0.0015</t>
-  </si>
-  <si>
-    <t>0.0223,0.0272,0.9513,0.0015</t>
-  </si>
-  <si>
-    <t>0.0013,0.0165,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0213,0.9767,0.0052</t>
-  </si>
-  <si>
-    <t>0.0234,0.0267,0.9540,0.0050</t>
-  </si>
-  <si>
-    <t>0.9773,0.0007,0.0169,0.0010</t>
-  </si>
-  <si>
-    <t>0.9688,0.0004,0.0407,0.0005</t>
-  </si>
-  <si>
-    <t>0.8830,0.0209,0.1154,0.0043</t>
-  </si>
-  <si>
-    <t>0.9912,0.0061,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9936,0.0072,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9938,0.0068,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0121,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0074,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9736,0.0510,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0021,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0481,0.0608,0.8789,0.0042</t>
-  </si>
-  <si>
-    <t>0.0164,0.0546,0.9841,0.0004</t>
-  </si>
-  <si>
-    <t>0.0092,0.0860,0.9584,0.0020</t>
-  </si>
-  <si>
-    <t>0.1119,0.0354,0.8763,0.0045</t>
-  </si>
-  <si>
-    <t>0.0242,0.0029,0.9817,0.0011</t>
-  </si>
-  <si>
-    <t>0.0727,0.0054,0.9637,0.0016</t>
-  </si>
-  <si>
-    <t>0.0766,0.0140,0.8656,0.0518</t>
-  </si>
-  <si>
-    <t>0.1560,0.0012,0.8843,0.0023</t>
-  </si>
-  <si>
-    <t>0.9527,0.0012,0.0010,0.0392</t>
-  </si>
-  <si>
-    <t>0.0528,0.0271,0.0079,0.9651</t>
-  </si>
-  <si>
-    <t>0.1150,0.0022,0.0022,0.9461</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.0019,0.9963</t>
-  </si>
-  <si>
-    <t>0.0061,0.0012,0.0018,0.9949</t>
-  </si>
-  <si>
-    <t>0.9345,0.0146,0.0142,0.0168</t>
+    <t>0.9942,0.0014,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0053,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0071,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9744,0.0298,0.0041,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0025,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.0360,0.9873,0.0098</t>
+  </si>
+  <si>
+    <t>0.0385,0.0923,0.9489,0.0047</t>
+  </si>
+  <si>
+    <t>0.8875,0.0140,0.0883,0.0053</t>
+  </si>
+  <si>
+    <t>0.0056,0.0018,0.9929,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0465,0.9961,0.0025</t>
+  </si>
+  <si>
+    <t>0.0447,0.2263,0.8461,0.0151</t>
+  </si>
+  <si>
+    <t>0.0014,0.0083,0.9955,0.0026</t>
+  </si>
+  <si>
+    <t>0.0533,0.1238,0.7680,0.0029</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.9972,0.0007</t>
+  </si>
+  <si>
+    <t>0.0126,0.0199,0.9742,0.0038</t>
+  </si>
+  <si>
+    <t>0.0188,0.0192,0.9705,0.0033</t>
+  </si>
+  <si>
+    <t>0.9696,0.0014,0.0243,0.0013</t>
+  </si>
+  <si>
+    <t>0.9858,0.0003,0.0221,0.0002</t>
+  </si>
+  <si>
+    <t>0.8906,0.0462,0.0672,0.0058</t>
+  </si>
+  <si>
+    <t>0.9939,0.0034,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9930,0.0117,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0041,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9773,0.0318,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0029,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0748,0.0157,0.9367,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.1339,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0144,0.9905,0.0009</t>
+  </si>
+  <si>
+    <t>0.0822,0.0065,0.9339,0.0029</t>
+  </si>
+  <si>
+    <t>0.0059,0.0011,0.9952,0.0004</t>
+  </si>
+  <si>
+    <t>0.0201,0.0029,0.9719,0.0142</t>
+  </si>
+  <si>
+    <t>0.0418,0.0099,0.9532,0.0062</t>
+  </si>
+  <si>
+    <t>0.0857,0.0048,0.8953,0.0071</t>
+  </si>
+  <si>
+    <t>0.9462,0.0158,0.0057,0.0184</t>
+  </si>
+  <si>
+    <t>0.1326,0.0137,0.0019,0.9370</t>
+  </si>
+  <si>
+    <t>0.0397,0.0085,0.0054,0.9750</t>
+  </si>
+  <si>
+    <t>0.0123,0.0003,0.0011,0.9942</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0008,0.9981</t>
+  </si>
+  <si>
+    <t>0.9196,0.0169,0.0083,0.0356</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2368,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3586,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,10 +3953,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,10 +4121,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4664,7 +4670,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
